--- a/Assets/asoliddev - Auto Chess/Config/BuffConfig.xlsx
+++ b/Assets/asoliddev - Auto Chess/Config/BuffConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\project\unity\auto-chess\Assets\asoliddev - Auto Chess\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB07C0E8-18BC-45DF-BCC8-0CBB48717F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAA920E-6326-456A-A97D-F3B04AC6E1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40275" yWindow="-1035" windowWidth="28800" windowHeight="27285" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-3720" windowWidth="57840" windowHeight="32040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseBuffData" sheetId="1" r:id="rId1"/>
@@ -336,1135 +336,1110 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>移动</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击倍数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害倍率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害倍率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>动力失效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宕机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器失效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝对防御</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>des</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxArmor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机体值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>addRange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能范围增强</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>electricPower</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供电力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>armorRegeneration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲恢复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>physicalDamage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理属性伤害增强</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireDamage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧属性伤害增强</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iceDamage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻属性伤害增强</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lightingDamage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电击属性伤害增强</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>acidDamage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酸蚀属性伤害增强</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理属性伤害减免</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧属性伤害减免</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻属性伤害减免</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电击属性伤害减免</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酸蚀属性伤害减免</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxMana</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能源值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaRegeneration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能源恢复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxMana + 30,manaRegeneration + 3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeHit</t>
+  </si>
+  <si>
+    <t>{int buff_ID,float odds,string targetType}[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>三零重工1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三零重工2</t>
+  </si>
+  <si>
+    <t>三零重工3</t>
+  </si>
+  <si>
+    <t>海力克斯1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>海力克斯2</t>
+  </si>
+  <si>
+    <t>海力克斯3</t>
+  </si>
+  <si>
+    <t>射线巫师1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>射线巫师2</t>
+  </si>
+  <si>
+    <t>射线巫师3</t>
+  </si>
+  <si>
+    <t>军用武装1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>军用武装2</t>
+  </si>
+  <si>
+    <t>军用武装3</t>
+  </si>
+  <si>
+    <t>新世纪材料1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新世纪材料2</t>
+  </si>
+  <si>
+    <t>新世纪材料3</t>
+  </si>
+  <si>
+    <t>宇航协会1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宇航协会2</t>
+  </si>
+  <si>
+    <t>宇航协会3</t>
+  </si>
+  <si>
+    <t>机械工程1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械工程2</t>
+  </si>
+  <si>
+    <t>光学1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>光学2</t>
+  </si>
+  <si>
+    <t>电子学1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电子学2</t>
+  </si>
+  <si>
+    <t>人工智能1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>动力学1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>动力学2</t>
+  </si>
+  <si>
+    <t>材料学1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料学2</t>
+  </si>
+  <si>
+    <t>castDelay</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chargingDelay</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>充能延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>castDelay * -0.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>castDelay * -0.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击命中率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hitRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeCast</t>
+  </si>
+  <si>
+    <t>BeforeCast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterCast</t>
+  </si>
+  <si>
+    <t>AfterCast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法前触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法后触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterCrit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterDodge</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击后触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避后触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxArmor + 30,maxHealth + 20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxArmor + 60,maxHealth + 40</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxArmor + 120,maxHealth + 80</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxMana + 50,manaRegeneration + 6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxMana + 80,manaRegeneration + 10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲和机体提升</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能源学1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素伤害提升</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击后，有几率提升伤害抗性并增强恢复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升伤害抗性并增强恢复</t>
+  </si>
+  <si>
+    <t>提升暴击几率和伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能源和能源恢复提升</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireDamage * 0.3,iceDamage * 0.3,lightingDamage * 0.3,acidDamage * 0.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireDamage * 0.5,iceDamage * 0.5,lightingDamage * 0.5,acidDamage * 0.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireDamage * 0.8,iceDamage * 0.8,lightingDamage * 0.8,acidDamage * 0.8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>间隔减少施法延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少施法延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击时有概率减少目标伤害抗性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少目标伤害抗性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击时增加目标充能延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升伤害抗性并增强恢复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能源学2</t>
+  </si>
+  <si>
+    <t>枪械1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪械2</t>
+  </si>
+  <si>
+    <t>战斗结束后恢复机体值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>支援机伤害增加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击后增加物理伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加充能延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>反弹受到的伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterHit</t>
+  </si>
+  <si>
+    <t>反击1</t>
+  </si>
+  <si>
+    <t>反击2</t>
+  </si>
+  <si>
+    <t>反击3</t>
+  </si>
+  <si>
+    <t>松野会社-反击1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>松野会社-反击2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>松野会社-反击3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新世纪材料-修复1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新世纪材料-修复2</t>
+  </si>
+  <si>
+    <t>新世纪材料-修复3</t>
+  </si>
+  <si>
+    <t>机械工程-加速1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械工程-加速2</t>
+  </si>
+  <si>
+    <t>光学-熔融洞穿1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>光学-熔融洞穿2</t>
+  </si>
+  <si>
+    <t>电子学-电路干扰1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电子学-电路干扰2</t>
+  </si>
+  <si>
+    <t>BeforeAttack</t>
+  </si>
+  <si>
+    <t>BeforeAttack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterAttack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击前触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击后触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterDodge</t>
+  </si>
+  <si>
+    <t>闪避提升</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>松野会社-闪避1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>松野会社-闪避2</t>
+  </si>
+  <si>
+    <t>松野会社-闪避3</t>
+  </si>
+  <si>
+    <t>30,0.3,Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>31,0.4,Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>32,0.5,Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>38,1,Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>39,1,Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>42,1,Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>43,1,Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>46,0.2,Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>47,0.3,Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能有概率额外释放一次</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>physicalDamage + 10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避后下一次攻击物理伤害增加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次攻击物理伤害增加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chargingDelay + 0.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chargingDelay + 0.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤支援机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>physicalDamage + 12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>physicalDamage + 15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>physicalDamage + 2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>physicalDamage + 3</t>
+  </si>
+  <si>
+    <t>BeforeBattle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterBattle</t>
+  </si>
+  <si>
+    <t>AfterBattle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗前触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗后触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21,1,Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>22,1,Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>23,1,Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>24,1,Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,1,Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26,1,Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗加成1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加伤害,减少受到的伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗加成2</t>
+  </si>
+  <si>
+    <t>战斗加成3</t>
+  </si>
+  <si>
+    <t>战斗加成4</t>
+  </si>
+  <si>
+    <t>manaRegeneration + 30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaRegeneration + 50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>armorRegeneration + 60</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧急修复 Lvl.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复少量护甲值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧急修复 Lvl.2</t>
+  </si>
+  <si>
+    <t>回复中量护甲值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复大量护甲值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>armorRegeneration + 30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>armorRegeneration + 100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复少量能源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复中量能源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复大量能源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaRegeneration + 20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaRegeneration + 35</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaRegeneration + 60</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧急修复 Lvl.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧急能源回收 Lvl.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧急能源回收 Lvl.2</t>
+  </si>
+  <si>
+    <t>紧急能源回收 Lvl.3</t>
+  </si>
+  <si>
+    <t>修复 Lvl.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复 Lvl.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复 Lvl.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能源回收 Lvl.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能源回收 Lvl.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能源回收 Lvl.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缓慢回复少量护甲值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缓慢回复中量护甲值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缓慢回复大量护甲值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缓慢回复少量能源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缓慢回复中量能源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缓慢回复大量能源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>armorRegeneration + 8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>armorRegeneration + 24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>armorRegeneration + 16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaRegeneration + 6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaRegeneration + 12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围修复 Lvl.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围修复 Lvl.2</t>
+  </si>
+  <si>
+    <t>范围修复 Lvl.3</t>
+  </si>
+  <si>
+    <t>范围能源回收 Lvl.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围能源回收 Lvl.2</t>
+  </si>
+  <si>
+    <t>范围能源回收 Lvl.3</t>
+  </si>
+  <si>
+    <t>armorRegeneration + 15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>armorRegeneration + 50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaRegeneration + 15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲刺 Lvl.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲刺 Lvl.2</t>
+  </si>
+  <si>
+    <t>冲刺 Lvl.3</t>
+  </si>
+  <si>
+    <t>增加少量移速,减少受到的伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加中量移速,减少受到的伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加大量移速,减少受到的伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过载 lvl.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过载 lvl.2</t>
+  </si>
+  <si>
+    <t>过载 lvl.3</t>
+  </si>
+  <si>
+    <t>减少少量施法延迟和充能延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少中量施法延迟和充能延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少大量施法延迟和充能延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰护盾-减速 Lvl.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰护盾-减速 Lvl.2</t>
+  </si>
+  <si>
+    <t>寒冰护盾-减速 Lvl.3</t>
+  </si>
+  <si>
+    <t>减少移动速度并增加施法延迟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>castDelay - 0.8,chargingDelay * -0,2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>castDelay - 1.2,chargingDelay * -0,3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>castDelay - 1.7,chargingDelay * -0,4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>moveSpeed * -0.2,castDelay * 0.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>moveSpeed * -0.3,castDelay * 0.6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>moveSpeed * -0.4,castDelay * 0.7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒受到伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冻结</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>短路</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>腐蚀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少伤害抗性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒减少能量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaRegeneration - 2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>moveSpeed * -0.1,castDelay * 0.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BurnBuffBehaviour</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CorrosionBuffBehaviour</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FreezeBuffBehaviour</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShortCircuitBuffBehaviour</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复机体</t>
+  </si>
+  <si>
+    <t>维修</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>armorRegeneration + 4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dodgeChange * -0.2</t>
+  </si>
+  <si>
+    <t>dodgeChange * -0.3</t>
+  </si>
+  <si>
+    <t>dodgeChange * -0.4</t>
+  </si>
+  <si>
     <t>takeDamageMultiple</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>applyDamageMultiple</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击倍数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成的伤害倍率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害倍率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>动力失效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>宕机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器失效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>绝对防御</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>des</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxArmor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>护盾值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>机体值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>addRange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能范围增强</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>electricPower</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提供电力</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>armorRegeneration</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>护甲恢复</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>physicalDamage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理属性伤害增强</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fireDamage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧属性伤害增强</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>iceDamage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻属性伤害增强</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>lightingDamage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>电击属性伤害增强</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>acidDamage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>酸蚀属性伤害增强</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理属性伤害减免</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧属性伤害减免</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻属性伤害减免</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>电击属性伤害减免</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>酸蚀属性伤害减免</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxMana</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能源值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能源恢复</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxMana + 30,manaRegeneration + 3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeHit</t>
-  </si>
-  <si>
-    <t>{int buff_ID,float odds,string targetType}[]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Interval</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Layer</t>
-  </si>
-  <si>
-    <t>三零重工1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>三零重工2</t>
-  </si>
-  <si>
-    <t>三零重工3</t>
-  </si>
-  <si>
-    <t>海力克斯1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>海力克斯2</t>
-  </si>
-  <si>
-    <t>海力克斯3</t>
-  </si>
-  <si>
-    <t>射线巫师1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>射线巫师2</t>
-  </si>
-  <si>
-    <t>射线巫师3</t>
-  </si>
-  <si>
-    <t>军用武装1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>军用武装2</t>
-  </si>
-  <si>
-    <t>军用武装3</t>
-  </si>
-  <si>
-    <t>新世纪材料1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新世纪材料2</t>
-  </si>
-  <si>
-    <t>新世纪材料3</t>
-  </si>
-  <si>
-    <t>宇航协会1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>宇航协会2</t>
-  </si>
-  <si>
-    <t>宇航协会3</t>
-  </si>
-  <si>
-    <t>机械工程1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>机械工程2</t>
-  </si>
-  <si>
-    <t>光学1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>光学2</t>
-  </si>
-  <si>
-    <t>电子学1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>电子学2</t>
-  </si>
-  <si>
-    <t>人工智能1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>动力学1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>动力学2</t>
-  </si>
-  <si>
-    <t>材料学1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>材料学2</t>
-  </si>
-  <si>
-    <t>castDelay</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>chargingDelay</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>施法延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>充能延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>castDelay * -0.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>castDelay * -0.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>受击命中率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hitRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hitRate * -0.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hitRate * -0.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hitRate * -0.4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>applyDamageMultiple * -0.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>applyDamageMultiple * -0.4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>applyDamageMultiple * -0.2,armorRegeneration + 4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>applyDamageMultiple * -0.3,armorRegeneration + 7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>applyDamageMultiple * -0.4,armorRegeneration + 10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nonCritChange</t>
-  </si>
-  <si>
-    <t>nonCritChange * -0.1,critMultiple + 0.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nonCritChange * -0.15,critMultiple + 0.8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nonCritChange * -0.2,critMultiple + 1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeCast</t>
-  </si>
-  <si>
-    <t>BeforeCast</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterCast</t>
-  </si>
-  <si>
-    <t>AfterCast</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>施法前触发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>施法后触发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterCrit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterDodge</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击后触发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪避后触发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxArmor + 30,maxHealth + 20</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxArmor + 60,maxHealth + 40</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxArmor + 120,maxHealth + 80</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxMana + 50,manaRegeneration + 6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxMana + 80,manaRegeneration + 10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>护甲和机体提升</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能源学1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素伤害提升</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到攻击后，有几率提升伤害抗性并增强恢复</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升伤害抗性并增强恢复</t>
-  </si>
-  <si>
-    <t>提升暴击几率和伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能源和能源恢复提升</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fireDamage * 0.3,iceDamage * 0.3,lightingDamage * 0.3,acidDamage * 0.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fireDamage * 0.5,iceDamage * 0.5,lightingDamage * 0.5,acidDamage * 0.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fireDamage * 0.8,iceDamage * 0.8,lightingDamage * 0.8,acidDamage * 0.8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>间隔减少施法延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少施法延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时有概率减少目标伤害抗性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少目标伤害抗性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时增加目标充能延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升伤害抗性并增强恢复</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能源学2</t>
-  </si>
-  <si>
-    <t>枪械1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>枪械2</t>
-  </si>
-  <si>
-    <t>战斗结束后恢复机体值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>支援机伤害增加</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击后增加物理伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加充能延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>反弹受到的伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterHit</t>
-  </si>
-  <si>
-    <t>反击1</t>
-  </si>
-  <si>
-    <t>反击2</t>
-  </si>
-  <si>
-    <t>反击3</t>
-  </si>
-  <si>
-    <t>松野会社-反击1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>松野会社-反击2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>松野会社-反击3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新世纪材料-修复1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新世纪材料-修复2</t>
-  </si>
-  <si>
-    <t>新世纪材料-修复3</t>
-  </si>
-  <si>
-    <t>机械工程-加速1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>机械工程-加速2</t>
-  </si>
-  <si>
-    <t>光学-熔融洞穿1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>光学-熔融洞穿2</t>
-  </si>
-  <si>
-    <t>电子学-电路干扰1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>电子学-电路干扰2</t>
-  </si>
-  <si>
-    <t>BeforeAttack</t>
-  </si>
-  <si>
-    <t>BeforeAttack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterAttack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击前触发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击后触发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterDodge</t>
-  </si>
-  <si>
-    <t>闪避提升</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>松野会社-闪避1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>松野会社-闪避2</t>
-  </si>
-  <si>
-    <t>松野会社-闪避3</t>
-  </si>
-  <si>
-    <t>30,0.3,Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>31,0.4,Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>32,0.5,Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>38,1,Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>39,1,Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>42,1,Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>43,1,Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>46,0.2,Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>47,0.3,Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能有概率额外释放一次</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>physicalDamage + 10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪避后下一次攻击物理伤害增加</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一次攻击物理伤害增加</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>chargingDelay + 0.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>chargingDelay + 0.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>召唤支援机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>physicalDamage + 12</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>physicalDamage + 15</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>physicalDamage + 2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>physicalDamage + 3</t>
-  </si>
-  <si>
-    <t>BeforeBattle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterBattle</t>
-  </si>
-  <si>
-    <t>AfterBattle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗前触发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗后触发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21,1,Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>22,1,Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>23,1,Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>24,1,Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>25,1,Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>26,1,Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>physicalDamageApplyRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fireDamageApplyRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>iceDamageApplyRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>lightingDamageApplyRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>acidDamageApplyRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗加成1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加伤害,减少受到的伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗加成2</t>
-  </si>
-  <si>
-    <t>战斗加成3</t>
-  </si>
-  <si>
-    <t>战斗加成4</t>
-  </si>
-  <si>
-    <t>takeDamageMultiple * 0.03,applyDamageMultiple * -0.03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>takeDamageMultiple * 0.05,applyDamageMultiple * -0.05</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>takeDamageMultiple * 0.08,applyDamageMultiple * -0.08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>takeDamageMultiple * 0.12,applyDamageMultiple * -0.12</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>moveSpeed * 0.3,applyDamageMultiple * -0.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration + 30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration + 50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>armorRegeneration + 60</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>紧急修复 Lvl.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复少量护甲值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>紧急修复 Lvl.2</t>
-  </si>
-  <si>
-    <t>回复中量护甲值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复大量护甲值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>armorRegeneration + 30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>armorRegeneration + 100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复少量能源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复中量能源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复大量能源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration + 20</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration + 35</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration + 60</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>紧急修复 Lvl.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>紧急能源回收 Lvl.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>紧急能源回收 Lvl.2</t>
-  </si>
-  <si>
-    <t>紧急能源回收 Lvl.3</t>
-  </si>
-  <si>
-    <t>修复 Lvl.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>修复 Lvl.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>修复 Lvl.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能源回收 Lvl.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能源回收 Lvl.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能源回收 Lvl.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>缓慢回复少量护甲值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>缓慢回复中量护甲值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>缓慢回复大量护甲值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>缓慢回复少量能源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>缓慢回复中量能源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>缓慢回复大量能源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>armorRegeneration + 8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>armorRegeneration + 24</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>armorRegeneration + 16</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration + 6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration + 12</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>范围修复 Lvl.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>范围修复 Lvl.2</t>
-  </si>
-  <si>
-    <t>范围修复 Lvl.3</t>
-  </si>
-  <si>
-    <t>范围能源回收 Lvl.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>范围能源回收 Lvl.2</t>
-  </si>
-  <si>
-    <t>范围能源回收 Lvl.3</t>
-  </si>
-  <si>
-    <t>armorRegeneration + 15</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>armorRegeneration + 50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration + 15</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲刺 Lvl.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲刺 Lvl.2</t>
-  </si>
-  <si>
-    <t>冲刺 Lvl.3</t>
-  </si>
-  <si>
-    <t>增加少量移速,减少受到的伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加中量移速,减少受到的伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加大量移速,减少受到的伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>moveSpeed * 0.2,applyDamageMultiple * -0.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>moveSpeed * 0.5,applyDamageMultiple * -0.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>过载 lvl.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>过载 lvl.2</t>
-  </si>
-  <si>
-    <t>过载 lvl.3</t>
-  </si>
-  <si>
-    <t>减少少量施法延迟和充能延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少中量施法延迟和充能延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少大量施法延迟和充能延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒冰护盾-减速 Lvl.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒冰护盾-减速 Lvl.2</t>
-  </si>
-  <si>
-    <t>寒冰护盾-减速 Lvl.3</t>
-  </si>
-  <si>
-    <t>减少移动速度并增加施法延迟</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>castDelay - 0.8,chargingDelay * -0,2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>castDelay - 1.2,chargingDelay * -0,3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>castDelay - 1.7,chargingDelay * -0,4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>moveSpeed * -0.2,castDelay * 0.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>moveSpeed * -0.3,castDelay * 0.6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>moveSpeed * -0.4,castDelay * 0.7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每秒受到伤害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冻结</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>短路</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>腐蚀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少伤害抗性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每秒减少能量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>manaRegeneration - 2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>applyDamageMultiple + 0.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>moveSpeed * -0.1,castDelay * 0.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BurnBuffBehaviour</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CorrosionBuffBehaviour</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FreezeBuffBehaviour</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShortCircuitBuffBehaviour</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复机体</t>
-  </si>
-  <si>
-    <t>维修</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>armorRegeneration + 4</t>
+  </si>
+  <si>
+    <t>damageDefenceRate</t>
+  </si>
+  <si>
+    <t>damageDefenceRate * -0.2,armorRegeneration + 4</t>
+  </si>
+  <si>
+    <t>damageDefenceRate * -0.3,armorRegeneration + 7</t>
+  </si>
+  <si>
+    <t>damageDefenceRate * -0.4,armorRegeneration + 10</t>
+  </si>
+  <si>
+    <t>damageDefenceRate * -0.2</t>
+  </si>
+  <si>
+    <t>damageDefenceRate * -0.4</t>
+  </si>
+  <si>
+    <t>takeDamageMultiple * 0.03,damageDefenceRate * -0.03</t>
+  </si>
+  <si>
+    <t>takeDamageMultiple * 0.05,damageDefenceRate * -0.05</t>
+  </si>
+  <si>
+    <t>takeDamageMultiple * 0.08,damageDefenceRate * -0.08</t>
+  </si>
+  <si>
+    <t>takeDamageMultiple * 0.12,damageDefenceRate * -0.12</t>
+  </si>
+  <si>
+    <t>moveSpeed * 0.2,damageDefenceRate * -0.1</t>
+  </si>
+  <si>
+    <t>moveSpeed * 0.3,damageDefenceRate * -0.1</t>
+  </si>
+  <si>
+    <t>moveSpeed * 0.5,damageDefenceRate * -0.1</t>
+  </si>
+  <si>
+    <t>damageDefenceRate + 0.2</t>
+  </si>
+  <si>
+    <t>physicalDefenceRate</t>
+  </si>
+  <si>
+    <t>fireDefenceRate</t>
+  </si>
+  <si>
+    <t>iceDefenceRate</t>
+  </si>
+  <si>
+    <t>lightingDefenceRate</t>
+  </si>
+  <si>
+    <t>acidDefenceRate</t>
+  </si>
+  <si>
+    <t>critChange</t>
+  </si>
+  <si>
+    <t>critChange * -0.1,critMultiple + 0.5</t>
+  </si>
+  <si>
+    <t>critChange * -0.15,critMultiple + 0.8</t>
+  </si>
+  <si>
+    <t>critChange * -0.2,critMultiple + 1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1856,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
@@ -1902,7 +1877,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1948,7 +1923,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -1975,7 +1950,7 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>25</v>
@@ -1999,7 +1974,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -2052,7 +2027,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -2105,7 +2080,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2129,10 +2104,10 @@
         <v>46</v>
       </c>
       <c r="N6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="O6" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="P6" t="s">
         <v>42</v>
@@ -2158,7 +2133,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -2182,10 +2157,10 @@
         <v>46</v>
       </c>
       <c r="N7" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="O7" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="R7" t="s">
         <v>49</v>
@@ -2229,18 +2204,18 @@
         <v>46</v>
       </c>
       <c r="N8" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="O8" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="N9" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="O9" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
@@ -2248,10 +2223,10 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -2286,10 +2261,10 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -2324,10 +2299,10 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -2351,10 +2326,10 @@
         <v>38</v>
       </c>
       <c r="N12" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="O12" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
@@ -2362,10 +2337,10 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -2389,10 +2364,10 @@
         <v>38</v>
       </c>
       <c r="N13" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="O13" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
@@ -2400,10 +2375,10 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -2427,10 +2402,10 @@
         <v>38</v>
       </c>
       <c r="N14" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="O14" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
@@ -2438,10 +2413,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -2465,10 +2440,10 @@
         <v>38</v>
       </c>
       <c r="N15" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="O15" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
@@ -2476,10 +2451,10 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C16" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D16">
         <v>-1</v>
@@ -2508,10 +2483,10 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D17">
         <v>-1</v>
@@ -2540,10 +2515,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D18">
         <v>-1</v>
@@ -2572,10 +2547,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D19">
         <v>-1</v>
@@ -2604,10 +2579,10 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2636,10 +2611,10 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2668,10 +2643,10 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="C22" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D22">
         <v>-1</v>
@@ -2695,7 +2670,7 @@
         <v>38</v>
       </c>
       <c r="L22" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -2703,10 +2678,10 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="C23" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -2730,7 +2705,7 @@
         <v>38</v>
       </c>
       <c r="L23" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -2738,10 +2713,10 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C24" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D24">
         <v>-1</v>
@@ -2765,7 +2740,7 @@
         <v>38</v>
       </c>
       <c r="L24" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -2773,10 +2748,10 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C25" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D25">
         <v>-1</v>
@@ -2791,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="I25" t="s">
         <v>38</v>
@@ -2800,7 +2775,7 @@
         <v>38</v>
       </c>
       <c r="L25" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -2808,10 +2783,10 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C26" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D26">
         <v>-1</v>
@@ -2826,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="I26" t="s">
         <v>38</v>
@@ -2835,7 +2810,7 @@
         <v>38</v>
       </c>
       <c r="L26" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -2843,10 +2818,10 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C27" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D27">
         <v>-1</v>
@@ -2861,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="I27" t="s">
         <v>38</v>
@@ -2870,7 +2845,7 @@
         <v>38</v>
       </c>
       <c r="L27" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -2878,10 +2853,10 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C28" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D28">
         <v>-1</v>
@@ -2896,10 +2871,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="I28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J28" t="s">
         <v>38</v>
@@ -2910,10 +2885,10 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C29" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D29">
         <v>-1</v>
@@ -2928,10 +2903,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="I29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J29" t="s">
         <v>38</v>
@@ -2942,10 +2917,10 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="C30" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D30">
         <v>-1</v>
@@ -2960,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="I30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J30" t="s">
         <v>38</v>
@@ -2974,10 +2949,10 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D31">
         <v>-1</v>
@@ -2992,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I31" t="s">
         <v>38</v>
@@ -3001,7 +2976,7 @@
         <v>38</v>
       </c>
       <c r="L31" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -3009,10 +2984,10 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D32">
         <v>-1</v>
@@ -3027,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I32" t="s">
         <v>38</v>
@@ -3036,7 +3011,7 @@
         <v>38</v>
       </c>
       <c r="L32" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -3044,10 +3019,10 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D33">
         <v>-1</v>
@@ -3062,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I33" t="s">
         <v>38</v>
@@ -3071,7 +3046,7 @@
         <v>38</v>
       </c>
       <c r="L33" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -3079,10 +3054,10 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="C34" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -3111,10 +3086,10 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C35" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -3143,10 +3118,10 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C36" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -3175,10 +3150,10 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C37" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D37">
         <v>-1</v>
@@ -3207,10 +3182,10 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D38">
         <v>-1</v>
@@ -3239,10 +3214,10 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D39">
         <v>-1</v>
@@ -3271,10 +3246,10 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C41" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D41">
         <v>-1</v>
@@ -3289,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I41" t="s">
         <v>38</v>
@@ -3298,7 +3273,7 @@
         <v>38</v>
       </c>
       <c r="L41" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -3306,10 +3281,10 @@
         <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D42">
         <v>-1</v>
@@ -3324,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I42" t="s">
         <v>38</v>
@@ -3333,7 +3308,7 @@
         <v>38</v>
       </c>
       <c r="L42" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
@@ -3341,10 +3316,10 @@
         <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C43" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -3359,13 +3334,13 @@
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="I43" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
@@ -3373,10 +3348,10 @@
         <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -3391,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="I44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J44" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
@@ -3405,10 +3380,10 @@
         <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C45" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D45">
         <v>-1</v>
@@ -3423,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="I45" t="s">
         <v>38</v>
@@ -3432,7 +3407,7 @@
         <v>38</v>
       </c>
       <c r="L45" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
@@ -3440,10 +3415,10 @@
         <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D46">
         <v>-1</v>
@@ -3458,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="I46" t="s">
         <v>38</v>
@@ -3467,7 +3442,7 @@
         <v>38</v>
       </c>
       <c r="L46" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
@@ -3475,10 +3450,10 @@
         <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C47" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D47">
         <v>0.5</v>
@@ -3507,10 +3482,10 @@
         <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="C48" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D48">
         <v>0.8</v>
@@ -3539,10 +3514,10 @@
         <v>44</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D49">
         <v>-1</v>
@@ -3557,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="I49" t="s">
         <v>38</v>
@@ -3566,7 +3541,7 @@
         <v>38</v>
       </c>
       <c r="L49" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
@@ -3574,10 +3549,10 @@
         <v>45</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D50">
         <v>-1</v>
@@ -3592,16 +3567,16 @@
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="I50" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="J50" t="s">
         <v>38</v>
       </c>
       <c r="L50" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
@@ -3609,10 +3584,10 @@
         <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C51" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D51">
         <v>-1</v>
@@ -3641,10 +3616,10 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C52" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D52">
         <v>-1</v>
@@ -3673,10 +3648,10 @@
         <v>48</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C53" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D53">
         <v>-1</v>
@@ -3705,10 +3680,10 @@
         <v>49</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C54" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D54">
         <v>-1</v>
@@ -3737,10 +3712,10 @@
         <v>50</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C55" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D55">
         <v>-1</v>
@@ -3755,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="I55" t="s">
         <v>38</v>
@@ -3769,10 +3744,10 @@
         <v>51</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D56">
         <v>-1</v>
@@ -3787,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="I56" t="s">
         <v>38</v>
@@ -3801,10 +3776,10 @@
         <v>52</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D57">
         <v>-1</v>
@@ -3819,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="I57" t="s">
         <v>38</v>
@@ -3833,10 +3808,10 @@
         <v>53</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D58">
         <v>-1</v>
@@ -3851,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="I58" t="s">
         <v>38</v>
@@ -3865,10 +3840,10 @@
         <v>54</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C59" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D59">
         <v>-1</v>
@@ -3883,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="I59" t="s">
         <v>38</v>
@@ -3897,10 +3872,10 @@
         <v>55</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="C60" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D60">
         <v>-1</v>
@@ -3915,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="I60" t="s">
         <v>38</v>
@@ -3929,10 +3904,10 @@
         <v>56</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C61" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D61">
         <v>-1</v>
@@ -3947,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="I61" t="s">
         <v>38</v>
@@ -3961,10 +3936,10 @@
         <v>57</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C62" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D62">
         <v>-1</v>
@@ -3979,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="I62" t="s">
         <v>38</v>
@@ -3993,10 +3968,10 @@
         <v>58</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="C64" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="D64">
         <v>-1</v>
@@ -4025,10 +4000,10 @@
         <v>59</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="D65">
         <v>-1</v>
@@ -4057,10 +4032,10 @@
         <v>60</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="C66" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="D66">
         <v>-1</v>
@@ -4089,10 +4064,10 @@
         <v>61</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="C67" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="D67">
         <v>-1</v>
@@ -4124,10 +4099,10 @@
         <v>180</v>
       </c>
       <c r="B71" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="C71" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -4156,10 +4131,10 @@
         <v>181</v>
       </c>
       <c r="B72" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C72" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -4188,10 +4163,10 @@
         <v>182</v>
       </c>
       <c r="B73" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C73" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -4220,10 +4195,10 @@
         <v>183</v>
       </c>
       <c r="B74" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="C74" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -4252,10 +4227,10 @@
         <v>184</v>
       </c>
       <c r="B75" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="C75" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -4284,10 +4259,10 @@
         <v>185</v>
       </c>
       <c r="B76" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="C76" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -4316,10 +4291,10 @@
         <v>186</v>
       </c>
       <c r="B77" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="C77" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="D77">
         <v>5</v>
@@ -4348,10 +4323,10 @@
         <v>187</v>
       </c>
       <c r="B78" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="C78" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="D78">
         <v>5</v>
@@ -4380,10 +4355,10 @@
         <v>188</v>
       </c>
       <c r="B79" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="C79" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="D79">
         <v>5</v>
@@ -4412,10 +4387,10 @@
         <v>189</v>
       </c>
       <c r="B80" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="C80" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="D80">
         <v>5</v>
@@ -4444,10 +4419,10 @@
         <v>190</v>
       </c>
       <c r="B81" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="C81" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="D81">
         <v>5</v>
@@ -4476,10 +4451,10 @@
         <v>191</v>
       </c>
       <c r="B82" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="C82" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="D82">
         <v>5</v>
@@ -4508,10 +4483,10 @@
         <v>192</v>
       </c>
       <c r="B83" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C83" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4540,10 +4515,10 @@
         <v>193</v>
       </c>
       <c r="B84" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="C84" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -4572,10 +4547,10 @@
         <v>194</v>
       </c>
       <c r="B85" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="C85" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -4604,10 +4579,10 @@
         <v>195</v>
       </c>
       <c r="B86" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="C86" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -4636,10 +4611,10 @@
         <v>196</v>
       </c>
       <c r="B87" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="C87" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4668,10 +4643,10 @@
         <v>197</v>
       </c>
       <c r="B88" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="C88" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4700,10 +4675,10 @@
         <v>198</v>
       </c>
       <c r="B89" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
       <c r="C89" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="D89">
         <v>3</v>
@@ -4732,10 +4707,10 @@
         <v>199</v>
       </c>
       <c r="B90" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="C90" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -4764,10 +4739,10 @@
         <v>200</v>
       </c>
       <c r="B91" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="C91" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="D91">
         <v>3</v>
@@ -4796,10 +4771,10 @@
         <v>201</v>
       </c>
       <c r="B92" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="C92" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="D92">
         <v>-1</v>
@@ -4828,10 +4803,10 @@
         <v>202</v>
       </c>
       <c r="B93" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="C93" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="D93">
         <v>-1</v>
@@ -4860,10 +4835,10 @@
         <v>203</v>
       </c>
       <c r="B94" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="C94" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="D94">
         <v>-1</v>
@@ -4892,10 +4867,10 @@
         <v>204</v>
       </c>
       <c r="B95" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="C95" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -4924,10 +4899,10 @@
         <v>205</v>
       </c>
       <c r="B96" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="C96" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -4956,10 +4931,10 @@
         <v>206</v>
       </c>
       <c r="B97" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="C97" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -4988,10 +4963,10 @@
         <v>207</v>
       </c>
       <c r="B98" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="C98" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -5012,7 +4987,7 @@
         <v>42</v>
       </c>
       <c r="J98" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
@@ -5020,10 +4995,10 @@
         <v>301</v>
       </c>
       <c r="B100" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="C100" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
       <c r="D100">
         <v>8</v>
@@ -5038,16 +5013,16 @@
         <v>0</v>
       </c>
       <c r="H100" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I100" t="s">
         <v>42</v>
       </c>
       <c r="J100" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K100" t="s">
-        <v>368</v>
+        <v>341</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
@@ -5055,10 +5030,10 @@
         <v>302</v>
       </c>
       <c r="B101" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="C101" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="D101">
         <v>8</v>
@@ -5079,10 +5054,10 @@
         <v>42</v>
       </c>
       <c r="J101" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K101" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
@@ -5090,10 +5065,10 @@
         <v>303</v>
       </c>
       <c r="B102" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="C102" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="D102">
         <v>8</v>
@@ -5108,16 +5083,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I102" t="s">
         <v>42</v>
       </c>
       <c r="J102" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K102" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
@@ -5125,10 +5100,10 @@
         <v>304</v>
       </c>
       <c r="B103" t="s">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="C103" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="D103">
         <v>8</v>
@@ -5149,10 +5124,10 @@
         <v>42</v>
       </c>
       <c r="J103" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K103" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -5263,10 +5238,10 @@
         <v>73</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -5292,7 +5267,7 @@
         <v>76</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -5315,10 +5290,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -5344,7 +5319,7 @@
         <v>75</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -5367,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -5393,10 +5368,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -5423,13 +5398,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -5452,13 +5427,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -5481,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -5506,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -5535,13 +5510,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>172</v>
+        <v>372</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -5564,13 +5539,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>77</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -5593,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -5618,13 +5593,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -5647,13 +5622,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -5676,13 +5651,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>173</v>
+        <v>373</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -5705,13 +5680,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>374</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -5734,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>175</v>
+        <v>375</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -5759,13 +5734,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -5788,13 +5763,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>165</v>
+        <v>350</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -5817,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>166</v>
+        <v>351</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -5846,13 +5821,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -5875,13 +5850,13 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -5904,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -5929,13 +5904,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>169</v>
+        <v>354</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -5958,13 +5933,13 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>170</v>
+        <v>355</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>274</v>
+        <v>368</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -5987,21 +5962,21 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>171</v>
+        <v>356</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>275</v>
+        <v>369</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="I31" s="1" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -6024,13 +5999,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>277</v>
+        <v>371</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -6053,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -6076,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>167</v>
+        <v>357</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -6099,7 +6074,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>168</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -6122,7 +6097,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -6145,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -6168,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -6191,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -6214,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>283</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -6237,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>284</v>
+        <v>360</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -6260,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>285</v>
+        <v>361</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -6283,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>286</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -6306,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
@@ -6329,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
@@ -6352,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -6375,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -6398,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -6421,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -6444,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -6467,7 +6442,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -6490,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -6513,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
@@ -6536,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
@@ -6559,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
@@ -6582,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
@@ -6605,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
@@ -6628,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
@@ -6651,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
@@ -6674,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
@@ -6697,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
@@ -6720,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6743,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>287</v>
+        <v>364</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -6766,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -6789,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -6812,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -6835,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -6858,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
@@ -6881,7 +6856,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
@@ -6904,7 +6879,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
@@ -6927,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
@@ -6950,7 +6925,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>367</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
@@ -6973,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
